--- a/TIMES-NZ/v303/VT_TIMESNZ_RES.xlsx
+++ b/TIMES-NZ/v303/VT_TIMESNZ_RES.xlsx
@@ -1244,6 +1244,11 @@
           <t>GW</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>DAYNITE</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1266,6 +1271,11 @@
           <t>GW</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>DAYNITE</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1666,6 +1676,11 @@
           <t>GW</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>DAYNITE</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1688,6 +1703,11 @@
           <t>GW</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>DAYNITE</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1710,6 +1730,11 @@
           <t>GW</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>DAYNITE</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1732,6 +1757,11 @@
           <t>GW</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>DAYNITE</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1754,6 +1784,11 @@
           <t>GW</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>DAYNITE</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1776,6 +1811,11 @@
           <t>GW</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>DAYNITE</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1798,6 +1838,11 @@
           <t>GW</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>DAYNITE</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1820,6 +1865,11 @@
           <t>GW</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>DAYNITE</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1842,6 +1892,11 @@
           <t>GW</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>DAYNITE</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1864,6 +1919,11 @@
           <t>GW</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>DAYNITE</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1886,6 +1946,11 @@
           <t>GW</t>
         </is>
       </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>DAYNITE</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2286,6 +2351,11 @@
           <t>GW</t>
         </is>
       </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>DAYNITE</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2308,6 +2378,11 @@
           <t>GW</t>
         </is>
       </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>DAYNITE</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2330,6 +2405,11 @@
           <t>GW</t>
         </is>
       </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>DAYNITE</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2352,6 +2432,11 @@
           <t>GW</t>
         </is>
       </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>DAYNITE</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2374,6 +2459,11 @@
           <t>GW</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>DAYNITE</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2396,6 +2486,11 @@
           <t>GW</t>
         </is>
       </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>DAYNITE</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2418,6 +2513,11 @@
           <t>GW</t>
         </is>
       </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>DAYNITE</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2440,6 +2540,11 @@
           <t>GW</t>
         </is>
       </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>DAYNITE</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2460,6 +2565,11 @@
       <c r="D91" t="inlineStr">
         <is>
           <t>GW</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>DAYNITE</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10368,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BIM</t>
+          <t>BIMDD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -10285,7 +10395,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NGA</t>
+          <t>NGADD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -10301,11 +10411,6 @@
       <c r="E21" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>25.0</t>
         </is>
       </c>
     </row>
